--- a/data/raw/corpus_cao_ifc.xlsx
+++ b/data/raw/corpus_cao_ifc.xlsx
@@ -2,23 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corpus CAO-IFC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Corpus CAO-IFC'!$A$1:$K$58</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,60 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFACD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE0E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0FFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0FFE0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -89,70 +46,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -515,23 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-  </cols>
+  <dimension ref="A1:K77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>sa</t>
@@ -588,3114 +485,2960 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Tata Ultra Mega-01 (Mundra &amp; Anjar)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>25797</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Infra (Coal Power 4150MW)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2008-04-08</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>14 Jun 2011</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Displacement, water quality, fish populations, air emissions, habitats</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Fishworkers assoc. MASS. IFC US$450M.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Tata Ultra Mega-02 (Tragadi Village)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>25797</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Infra (Coal Power 4150MW)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2008-04-08</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>21 Apr 2016</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Water access, loss of livelihoods, fish/habitats, security forces</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Merged with Tata-01.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Daehan Wind Power (Tafila)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>35349</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Infra (Wind 51.75MW)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>16 Jun 2020</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Noise, shadow flicker, bird mortality, health &amp; safety</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Flag 2 + Flag 3</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>20-year PPA. Community member.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>LCT-02 (Lomé Container Terminal)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>29197</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Infra (Port/Terminal)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2011-01-06</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>16 Feb 2018</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Resettlement, livelihoods, labor, RAP non-compliance</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>35-year concession. Civil society org.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Bujagali Energy-04</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>24408</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Infra (Hydropower 250MW)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2007-04-26</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Mar 2011</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Worker injuries, labor conditions</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Merged with 06 &amp; 08.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Bujagali Energy-06</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>24408</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Infra (Hydropower 250MW)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2007-04-26</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>03 Apr 2013</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Unpaid wages (300+ workers)</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Chairman of workers association.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Bujagali Energy-07</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>24408</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Infra (Hydropower 250MW)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2007-04-26</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>~2015</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Community/labor (same project)</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Verify date on CAO page.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Bujagali Energy-08</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>24408</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Infra (Hydropower 250MW)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2007-04-26</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>06 Jun 2017</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Worker health &amp; safety, compensation for injuries</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Former employee of contractor.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Lonmin-02 (Marikana)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>24803</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Mining (Platinum)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2006-12-19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>15 Jun 2015</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Air/water pollution, living conditions, housing, labor</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>IFC US$100M + US$50M equity.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Zarafshan-01</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>44364</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Infra (Wind 500MW)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>25 Jul 2023</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Soil damage oil spills, dust/biodiversity, unfenced site</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Flag 2</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Herder/landlord. 111 turbines. Closed DR.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Delonex &amp; Africa Oil (Kerio Valley)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>33557, 36699</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Mining (Oil &amp; Gas)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2013-09-12, 2015-07-09</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>06 Aug 2019</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Lack of consultation, land/livelihood, breach IFC PS</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>IFC equity US$60M + US$50M.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Palma Guinée-01 (Sheraton Conakry)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>32408</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Guinea</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Infra (Hotel)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2013-06-03</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>18 Jan 2023</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Unpaid wages, union intimidation, mold, retaliation</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Loan prepaid Sep 2022.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Al Subh Solar / Sunrise / Rising Sun</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>39729, 39995, 39997</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Infra (Solar Power)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2017-07-20, 2017-07-20, 2017-07-20</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>17 Mar 2024</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Labor — non-renewal contract, unpaid dues, working conditions</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Former employee. Benban complex.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Falcon Ma'An Solar Power</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>35483</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Infra (Solar Power)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2014-09-16</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>~2019</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Community engagement discontinued, labor practices</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Discontinued CSR.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>CIFI / Hidro Santa Cruz</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>26031</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>FI → Infra (Hydropower)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>2008-05-15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>16 Jul 2015</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Community health, indigenous peoples, violence, coercion, loss of life</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Canbalam hydropower. Suspended 2012. Très sévère.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Karot Hydro-03 (Jhelum River)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>36008</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Infra (Hydropower 720MW)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2016-05-19</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>06 Jul 2020</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Working conditions, freedom of association, grievance mechanism</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>China Three Gorges. Merged Karot-02 &amp; 04.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Nachtigal Hydropower Co-01</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>37673</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Infra (Hydropower 420MW)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2018-07-19</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>19 Apr 2022</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Resettlement, livelihoods, compensation, sacred sites, GBVH</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>EDF/IFC. MIGA 13075.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Antalya Airport LTF</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>50035</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Infra (Airport)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>26 Jan 2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Displacement, inadequate compensation, coercion</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Fraport TAV. €300M + €250M B Loan.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Alto Maipo-01 (Cajón del Maipo)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>31632</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Infra (Hydropower 531MW)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>2013-10-24</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>24 Jan 2017</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Water shortage/contamination, noise, biodiversity, conflict, loss of life</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Merged with Alto Maipo-02. IFC US$150M.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Alto Maipo-02 (Cajón del Maipo)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>31632</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Infra (Hydropower 531MW)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>2013-10-24</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>~2019</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Same project, merged with Alto Maipo-01</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Merged.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KEB Hana / Suralaya (Java 9&amp;10 Coal)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>à vérifier (FI)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>FI → Infra (Coal Power)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>13 Sep 2023</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Air pollution, land acquisition, loss of income, intimidation</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Sub-project coal power.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Enso Albania-01 (Lengarica)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>30979</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Albania</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Infra (Hydropower 8.9MW)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>2011-09-28</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>22 Jun 2015</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Biodiversity, critical habitats, ecotourism livelihood, water, land</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Flag 2 + Flag 3</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Small hydro. IFC US$8.6M equity.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Reventazón HPP-01</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>31383</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Infra (Hydropower 305.5MW)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>2012-11-29</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>13 Sep 2016</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Biodiversity, natural habitats, environment, land acquisition</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Flag 2 + Flag 3</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>IFC US$100M A loan. Merged with HPP-02.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Reventazón HPP-02</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>31383</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Infra (Hydropower 305.5MW)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>2012-11-29</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>~2017</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Same project, merged with HPP-01</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Flag 2 + Flag 3</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Merged.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Chad-Cameroon Pipeline-03 (Doba)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Chad</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Infra (Pipeline)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Likely community displacement, pollution, compensation</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Famous pipeline case. Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Chad-Cameroon Pipeline-02 (Cameroon)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Infra (Pipeline)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Likely community/environmental impacts</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Same pipeline. Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>India: Vizhinjam-01 (Kerala)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Infra (Port)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Likely community displacement, fishing livelihoods</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Major port project. Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>India: Vizhinjam-02 (Kerala)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Infra (Port)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Same project as Vizhinjam-01</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>India: Vizhinjam-03 (Kerala)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Infra (Port)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Same project as Vizhinjam-01</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Bangladesh: United Ashuganj Energy</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Infra (Power Plant)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Likely community/environmental</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Verify IFC No and details.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Jordan: Alcazar Energy-01</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Infra (Solar/Energy)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>à vérifier sur page CAO</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Verify IFC No and details.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Benban Solar-03</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Infra (Solar Power)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Labor/community — Benban complex</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Benban Solar-05</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Infra (Solar Power)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Labor/community — Benban complex</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Benban Solar-07</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Infra (Solar Power)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Labor/community — Benban complex</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Egypt: Alex Dev Ltd-02 / Beni Suef</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Probablement Infra (Power)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Georgia: AGL-01 (Makhalakidzeebi)</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Probablement Infra</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>India: Infrastructure Fund-01 (Dhenkanal)</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Probably resettlement</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>India: DFCCIL-01</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Infra (Rail corridor)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Probably displacement</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Türkiye: Asyaport-01</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Infra (Port)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Guinea: Nedbank / Kintinian</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Guinea</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Mining via FI</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Nigeria: Eleme Fertilizer II-01</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Mining/Chemicals</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>Probably pollution/community</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Flag 2</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Nepal: Cable Car-01</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Nepal</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Mongolia: Oyu Tolgoi-01 (Khanbogd)</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Mining (Copper/Gold)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Community displacement, water, pastureland</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Famous case. Rio Tinto. Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Mongolia: Oyu Tolgoi-02 (Khanbogd)</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Mining (Copper/Gold)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Same project as OT-01</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Peru: Yanacocha-09 (Cajamarca)</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Mining (Gold)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Community opposition, water contamination</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Newmont. Famous case. Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Peru: Yanacocha-10 (Cajamarca)</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Mining (Gold)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>Same project as Yanacocha-09</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Flag 1 + Flag 2</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Verify IFC No.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Ukraine: Galnaftogaz (Kiev)</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Verify.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Brazil: Valor-01 (São Paulo)</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Probably FI</t>
         </is>
       </c>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J49" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>HORS SCOPE — Probablement FI.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Morocco: Zalagh-01 (Tiddas)</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Probably Agribusiness</t>
         </is>
       </c>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J50" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>HORS SCOPE — Probablement agribusiness.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Kenya: Bridge International Academies</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>HORS SCOPE — Éducation.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Indonesia: Financial Intermediary-01</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Financial Institutions</t>
         </is>
       </c>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>HORS SCOPE — FI pure.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Malaysia: BILT Paper-02 (Sipitang)</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Manufacturing (Paper)</t>
         </is>
       </c>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>HORS SCOPE — Manufacturing.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Colombia: Alqueria-01 (Cajica)</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Agribusiness (Dairy)</t>
         </is>
       </c>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J54" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>HORS SCOPE — Dairy.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Ecuador: Pronaca COVID-01</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Agribusiness</t>
         </is>
       </c>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K55" s="8" t="inlineStr">
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>HORS SCOPE — Agribusiness.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Cambodia: PSBC-02</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Cambodia</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Financial Institutions</t>
         </is>
       </c>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="K56" s="8" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>HORS SCOPE — FI.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Yemen: HSA Foods-01 (Ras Isa)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Agribusiness</t>
         </is>
       </c>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K57" s="8" t="inlineStr">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>HORS SCOPE — Agribusiness.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Nicaragua: Ingenio Montelimar-01</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Nicaragua</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Agribusiness (Sugar)</t>
         </is>
       </c>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>HORS SCOPE — Sugar.</t>
         </is>
@@ -3710,12 +3453,12 @@
       <c r="B59" t="n">
         <v>39102</v>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Hydropower 250MW</t>
         </is>
@@ -3725,16 +3468,18 @@
           <t>2018-03-08</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
         <is>
           <t>Flag 1</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3745,7 +3490,7 @@
       <c r="B60" t="n">
         <v>32874</v>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
@@ -3760,11 +3505,14 @@
           <t>2015-01-21</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3775,7 +3523,7 @@
       <c r="B61" t="n">
         <v>36402</v>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
@@ -3790,14 +3538,704 @@
           <t>2015-11-11</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Zhaoheng Hydropower Holdings (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>30266</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Hydropower (portfolio 682.7MW)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cheves Hydro (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>29405</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Hydropower 168MW</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2010-12-07</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Butwal Power Co / Andhi Khola (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>28083</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Hydropower (small, 9.4MW)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2010-05-13</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cullinan / Petra Diamonds (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>36729</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Mining (Diamonds)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Antares Minerals (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>28215</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Mining (Copper exploration)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2009-06-19</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEI Solar Power (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>30053</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Solar 24MW</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2013-02-22</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Solar Power Korat 1 (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>28842</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Solar 6MW</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2010-05-13</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Mersin International Port (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>33943</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2013-07-08</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Santa Marta International Terminal (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>28544</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2010-03-18</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TCE Ege Konteyner Terminal (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>29472</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2010-05-21</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GSPL (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>25637</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Gas pipeline</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2007-05-22</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Azura Edo IPP (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>32859</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Thermal (gas) 450MW</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Mocuba Solar (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>36787</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Solar 40MW</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2016-10-27</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dolovo Wind / Čibuk 1 (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>33839</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wind 158MW</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2017-10-06</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SMP Gold / Saza Makongolosi (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>27746</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mining (Gold exploration)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2010-01-22</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>E-Power S.A. (CONTRÔLE)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>27274</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thermal (HFO) 31.2MW</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2010-12-19</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Scrapé 2026-07-23 — projet contrôle sans plainte CAO trouvée (voir méthode dans la conversation)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>